--- a/Végleges/IP címek (1) (1).xlsx
+++ b/Végleges/IP címek (1) (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TÜRR\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{BF983DB3-C827-4DAA-A6DD-3453A7875516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36EE7845-34A8-491E-B76F-2E4D1D0532D3}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB7E8517-2E54-4A9A-B3B5-2F504A106194}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11265" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bajai telephely (Központ)" sheetId="3" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="193">
   <si>
     <t>Ipv4</t>
   </si>
@@ -68,9 +57,6 @@
     <t>vlan1</t>
   </si>
   <si>
-    <t>10.10.100.100</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
@@ -86,15 +72,9 @@
     <t>recepcio_nyomtato1</t>
   </si>
   <si>
-    <t>10.10.100.105</t>
-  </si>
-  <si>
     <t>recepcio_nyomtato2</t>
   </si>
   <si>
-    <t>10.10.100.106</t>
-  </si>
-  <si>
     <t>Tárgyaló</t>
   </si>
   <si>
@@ -158,30 +138,18 @@
     <t>gig1</t>
   </si>
   <si>
-    <t>10.10.100.73</t>
-  </si>
-  <si>
     <t>targyalo_sw2</t>
   </si>
   <si>
-    <t>10.10.100.75</t>
-  </si>
-  <si>
     <t>targyalo_wireless</t>
   </si>
   <si>
-    <t>10.10.100.69</t>
-  </si>
-  <si>
     <t>piheno_wireless</t>
   </si>
   <si>
     <t>recepcio_wireless</t>
   </si>
   <si>
-    <t>10.10.100.68</t>
-  </si>
-  <si>
     <t>targyalo_tablet1</t>
   </si>
   <si>
@@ -218,57 +186,36 @@
     <t>Nyomtato_Iroda1</t>
   </si>
   <si>
-    <t>10.10.100.54</t>
-  </si>
-  <si>
     <t>PC_Iroda2</t>
   </si>
   <si>
     <t>Nyomtato_Iroda2</t>
   </si>
   <si>
-    <t>10.10.100.53</t>
-  </si>
-  <si>
     <t>PC_Iroda4</t>
   </si>
   <si>
     <t>Nyomtato_iroda4</t>
   </si>
   <si>
-    <t>10.10.100.59</t>
-  </si>
-  <si>
     <t>PC_Iroda5</t>
   </si>
   <si>
     <t>Nyomtato_iroda5</t>
   </si>
   <si>
-    <t>10.10.100.49</t>
-  </si>
-  <si>
     <t>RG</t>
   </si>
   <si>
     <t>PC_RG</t>
   </si>
   <si>
-    <t>10.10.100.10</t>
-  </si>
-  <si>
     <t>Nyomtato_RG</t>
   </si>
   <si>
-    <t>10.10.100.5</t>
-  </si>
-  <si>
     <t>Server_RG</t>
   </si>
   <si>
-    <t>10.10.100.3</t>
-  </si>
-  <si>
     <t>Győr_Router</t>
   </si>
   <si>
@@ -329,21 +276,12 @@
     <t>Győr_SW1</t>
   </si>
   <si>
-    <t>172.16.1.34</t>
-  </si>
-  <si>
     <t>Győr_Irodai1 SW</t>
   </si>
   <si>
-    <t>172.16.1.35</t>
-  </si>
-  <si>
     <t>Győr_Iroda2 SW</t>
   </si>
   <si>
-    <t>172.16.1.36</t>
-  </si>
-  <si>
     <t>Győr_Iroda 1 PC</t>
   </si>
   <si>
@@ -365,9 +303,6 @@
     <t>Győr_Raktár Nyomtató</t>
   </si>
   <si>
-    <t>172.16.1.67</t>
-  </si>
-  <si>
     <t>Győr_Raktár PC1</t>
   </si>
   <si>
@@ -615,13 +550,70 @@
   </si>
   <si>
     <t>72.92.210.6/30</t>
+  </si>
+  <si>
+    <t>10.10.100.105/27</t>
+  </si>
+  <si>
+    <t>10.10.100.106/27</t>
+  </si>
+  <si>
+    <t>10.10.100.100/27</t>
+  </si>
+  <si>
+    <t>10.10.100.73/27</t>
+  </si>
+  <si>
+    <t>10.10.100.75/27</t>
+  </si>
+  <si>
+    <t>10.10.100.54/27</t>
+  </si>
+  <si>
+    <t>10.10.100.53/27</t>
+  </si>
+  <si>
+    <t>10.10.100.59/27</t>
+  </si>
+  <si>
+    <t>10.10.100.49/27</t>
+  </si>
+  <si>
+    <t>10.10.100.10/27</t>
+  </si>
+  <si>
+    <t>10.10.100.5/27</t>
+  </si>
+  <si>
+    <t>10.10.100.3/27</t>
+  </si>
+  <si>
+    <t>Sw_RG</t>
+  </si>
+  <si>
+    <t>10.10.100.2/27</t>
+  </si>
+  <si>
+    <t>172.16.1.66/27</t>
+  </si>
+  <si>
+    <t>172.16.1.67/27</t>
+  </si>
+  <si>
+    <t>172.16.1.34/27</t>
+  </si>
+  <si>
+    <t>172.16.1.35/27</t>
+  </si>
+  <si>
+    <t>172.16.1.36/27</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -847,7 +839,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -909,6 +901,27 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -924,19 +937,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -957,7 +964,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-téma">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1253,8 +1260,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8263A6BB-B1A9-48B3-9C01-A0B104726D87}">
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:E44"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -1263,16 +1270,16 @@
     <col min="5" max="5" width="20.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="E1" s="27"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -1289,7 +1296,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
@@ -1300,542 +1307,556 @@
         <v>8</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>9</v>
+        <v>176</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="10" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>43</v>
+        <v>11</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>39</v>
+        <v>11</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="3" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="9" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>59</v>
+        <v>179</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>62</v>
+        <v>180</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>65</v>
+        <v>181</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>68</v>
+        <v>182</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="18"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="3" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>73</v>
+        <v>184</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
-      <c r="B43" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>10</v>
+      <c r="B43" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="C44" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="E44" s="35" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1850,7 +1871,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E28"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
     <col min="2" max="3" width="22.42578125" bestFit="1" customWidth="1"/>
@@ -1858,16 +1879,16 @@
     <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="E1" s="27"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -1875,81 +1896,81 @@
       <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="22"/>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="24"/>
-    </row>
-    <row r="4" spans="1:5">
+        <v>63</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" s="31"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>80</v>
-      </c>
-      <c r="E4" s="24"/>
-    </row>
-    <row r="5" spans="1:5">
+        <v>65</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" s="31"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="24"/>
-    </row>
-    <row r="6" spans="1:5">
+        <v>67</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="31"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D6" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="25"/>
-    </row>
-    <row r="7" spans="1:5">
+        <v>69</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" s="32"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E9" s="20"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="E9" s="27"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>1</v>
       </c>
@@ -1966,252 +1987,252 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>98</v>
+        <v>191</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>100</v>
+        <v>192</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="3" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>96</v>
+        <v>188</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="3" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
@@ -2233,7 +2254,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5745176A-E3EE-4736-AEBC-6021C2097FDE}">
   <dimension ref="A1:I20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
@@ -2247,31 +2268,31 @@
     <col min="10" max="10" width="22.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-    </row>
-    <row r="2" spans="1:9">
+      <c r="D1" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
-      <c r="D2" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
+      <c r="D2" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>1</v>
       </c>
@@ -2285,366 +2306,366 @@
         <v>4</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>4</v>
       </c>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="4" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="4" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="4" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="4" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="26" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
+        <v>9</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>9</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="3" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G10" s="26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>116</v>
+      </c>
+      <c r="G10" s="22" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>116</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>116</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="3" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G13" s="26" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>116</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="16" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>124</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="11" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
       <c r="B16" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="26" t="s">
-        <v>153</v>
+        <v>9</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2659,8 +2680,8 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB4EDA30-41BE-4ECD-ACF0-05AACFC0DA8F}">
-  <dimension ref="A1:E51"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
     <col min="3" max="3" width="24.7109375" customWidth="1"/>
@@ -2668,16 +2689,16 @@
     <col min="5" max="5" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="20"/>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="E1" s="27"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
@@ -2694,374 +2715,373 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="3" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3" t="s">
-        <v>158</v>
+        <v>140</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="3" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="3" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="19" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3" t="s">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="3" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
       <c r="B17" s="3" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="3" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="3" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="3" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="3" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
-      <c r="B27" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="C27" s="28" t="s">
+      <c r="B27" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="C27" s="24" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" s="26" t="s">
-        <v>189</v>
-      </c>
-      <c r="E28" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="C29" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="E29" s="26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" ht="15"/>
+        <v>169</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C29" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="E29" s="22" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="D1:E1"/>
